--- a/assessment_forms/049_internal_wall_insulation_risk_assessment--assessment_forms.xlsx
+++ b/assessment_forms/049_internal_wall_insulation_risk_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>end_of_terrace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Semi-Detached</t>
+          <t>End of terrace</t>
         </is>
       </c>
     </row>
@@ -1545,46 +1545,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>end_of_terrace</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>End of terrace</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>building_type_choices</t>
+          <t>property_size_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>end_of_terrace</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>End of terrace</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>building_type_choices</t>
+          <t>property_size_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1596,46 +1596,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>wall_construction_type_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Solid</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>wall_construction_type_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>hollow</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Hollow</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>solid</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Solid</t>
+          <t>Composite</t>
         </is>
       </c>
     </row>
@@ -1664,46 +1664,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hollow</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hollow</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wall_construction_type_choices</t>
+          <t>wall_construction_materials_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>brick</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Brick</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>wall_construction_type_choices</t>
+          <t>wall_construction_materials_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>block</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Block</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>brick</t>
+          <t>concrete</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Concrete</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>plasterboard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Plasterboard</t>
         </is>
       </c>
     </row>
@@ -1749,44 +1749,10 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>concrete</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>wall_construction_materials_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>plasterboard</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Plasterboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>wall_construction_materials_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
